--- a/outputs/50768.xlsx
+++ b/outputs/50768.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -31,10 +31,13 @@
     <t xml:space="preserve">Liklihood</t>
   </si>
   <si>
-    <t xml:space="preserve">4, 6</t>
+    <t xml:space="preserve">4,6</t>
   </si>
   <si>
     <t xml:space="preserve">1, 3, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,3,5</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -426,7 +429,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:H16"/>
+  <dimension ref="A3:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.14"/>
@@ -522,7 +525,8 @@
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="8"/>
+      <c r="I12" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -546,7 +550,9 @@
       <c r="G14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="1"/>
